--- a/api_test_report.xlsx
+++ b/api_test_report.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Real server boot verified OK on port 46999</t>
+          <t>Real uvicorn boot verified</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Route present and import/server checks passed</t>
+          <t>Endpoint available</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Register user</t>
+          <t>Register a player account</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -594,7 +594,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>pytest test_register passed</t>
+          <t>pytest tests/test_auth.py::test_register</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Login user</t>
+          <t>Login and receive JWT</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -627,7 +627,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>pytest test_login passed</t>
+          <t>pytest tests/test_auth.py::test_login</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Read current user</t>
+          <t>Read authenticated user</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -660,7 +660,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>pytest test_me passed; invalid token also returned 401</t>
+          <t>pytest tests/test_auth.py::test_me</t>
         </is>
       </c>
     </row>
@@ -670,21 +670,21 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/games/</t>
+          <t>/api/v1/auth/me</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Create game</t>
+          <t>Reject invalid bearer token</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>pytest test_create_game passed</t>
+          <t>pytest tests/test_auth.py::test_invalid_token</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -713,11 +713,11 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>List games</t>
+          <t>Create tic-tac-toe game</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>pytest test_list_games passed</t>
+          <t>pytest tests/test_games.py::test_create_game</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/games/{game_id}</t>
+          <t>/api/v1/games/</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Get game</t>
+          <t>List authenticated user's games</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -759,7 +759,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>pytest test_get_game passed</t>
+          <t>pytest tests/test_games.py::test_list_games</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Update game</t>
+          <t>Get a game</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -792,7 +792,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>pytest test_update_game passed</t>
+          <t>pytest tests/test_games.py::test_get_game</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -812,11 +812,11 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Delete game</t>
+          <t>Update a game</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>pytest test_delete_game passed</t>
+          <t>pytest tests/test_games.py::test_update_game</t>
         </is>
       </c>
     </row>
@@ -835,30 +835,96 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/games/{game_id}</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Delete a game</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>pytest tests/test_games.py::test_delete_game</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>/api/v1/games/{game_id}</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Deleted game returns not found</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>pytest tests/test_games.py::test_delete_game</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>/api/v1/games/{game_id}/moves</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Make move</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Make next tic-tac-toe move</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>201</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>pytest test_make_move passed</t>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>pytest tests/test_games.py::test_make_move</t>
         </is>
       </c>
     </row>
